--- a/data/trans_orig/IP16A98-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A98-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16358</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20556</t>
+          <t>20566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33818</t>
+          <t>34065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40208</t>
+          <t>40766</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>25557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31809</t>
+          <t>32332</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22092</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>11282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>24222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37712</t>
+          <t>37238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45280</t>
+          <t>44901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40785</t>
+          <t>40724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50882</t>
+          <t>50888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82139</t>
+          <t>81394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94373</t>
+          <t>94334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>20588</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>27173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19321</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25456</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42672</t>
+          <t>42535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51298</t>
+          <t>51250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23887</t>
+          <t>24149</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30686</t>
+          <t>31428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30698</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50108</t>
+          <t>49638</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113311</t>
+          <t>113049</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>125785</t>
+          <t>125679</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>112582</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127550</t>
+          <t>126812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230358</t>
+          <t>230828</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>249768</t>
+          <t>250455</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24244</t>
+          <t>23723</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>31079</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18413</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22663</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29049</t>
+          <t>29453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17597</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22530</t>
+          <t>22563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32399</t>
+          <t>33070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41782</t>
+          <t>41457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30241</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58483</t>
+          <t>58450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70299</t>
+          <t>70044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34518</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21484</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28895</t>
+          <t>28145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>30417</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35241</t>
+          <t>35094</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55175</t>
+          <t>54222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>94675</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107994</t>
+          <t>107712</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>86873</t>
+          <t>86618</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>100668</t>
+          <t>101216</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>184680</t>
+          <t>185633</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>204614</t>
+          <t>204761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22137</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41526</t>
+          <t>41861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51905</t>
+          <t>52019</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19794</t>
+          <t>19722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23022</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39497</t>
+          <t>39946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45604</t>
+          <t>45581</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>28765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>45530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>47616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73170</t>
+          <t>73692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29171</t>
+          <t>31350</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46796</t>
+          <t>47235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87948</t>
+          <t>86695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119945</t>
+          <t>120324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25718</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33895</t>
+          <t>34200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47760</t>
+          <t>48004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58087</t>
+          <t>58213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21965</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>18614</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46297</t>
+          <t>48262</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47848</t>
+          <t>48145</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84570</t>
+          <t>85329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>157581</t>
+          <t>156773</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>133012</t>
+          <t>131047</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155588</t>
+          <t>154645</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>270127</t>
+          <t>269368</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>306849</t>
+          <t>306552</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A98-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A98-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4747</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4987</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5010</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4999</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19192</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16453</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21200</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18926</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15933</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20346</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15910</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20366</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19192</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16201</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20566</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,53%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34065</t>
+          <t>34207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40766</t>
+          <t>40692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21200</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21200</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21200</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>20920</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>20920</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>20920</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21200</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21200</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2804</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5748</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>47,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1369</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4249</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4167</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,32%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2804</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6010</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9284</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6340</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>52,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>20288</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17408</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17490</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>21657</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,68%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>80,76%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9284</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>6078</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11398</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>76,8%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>50,28%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>44</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25557</t>
+          <t>25794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>31842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>21657</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>21657</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>21657</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,67 +1413,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>33,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>1305</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3804</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3914</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>12,7%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4271</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11131</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8287</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>66,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8972</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6473</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6363</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>10277</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>87,3%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,98%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>61,92%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11131</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8207</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>65,77%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>29</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>16713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>22041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10277</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>10277</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>10277</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10389</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6061</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16070</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6632</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3742</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11405</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11393</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10389</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6085</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16249</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,24%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24222</t>
+          <t>24053</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46584</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>40903</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>50912</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>71,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>42011</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37238</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>44901</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>37250</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>45399</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>46584</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>50888</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,76%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81394</t>
+          <t>81563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94334</t>
+          <t>94409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>56973</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>56973</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>56973</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>48643</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>48643</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>48643</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>56973</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>56973</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>56973</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7641</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>28,58%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4226</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8057</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8233</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>14,75%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3389</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6904</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23344</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19092</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>25454</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,32%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>71,42%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>24419</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20588</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>27173</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>20412</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26689</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>85,25%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>71,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23344</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19829</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>25471</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,32%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42535</t>
+          <t>42665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51250</t>
+          <t>51216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>26733</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>26733</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26733</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>28645</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>28645</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>28645</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>26733</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>26733</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>26733</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>19,42%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>44,23%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4065</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>18,98%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>57,61%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2679</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5990</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>19,42%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -2550,74 +2550,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11116</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7694</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13053</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>80,58%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>55,77%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>5717</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2991</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2948</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>7056</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>81,02%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>42,39%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>41,77%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11116</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>7805</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>13103</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>80,58%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>56,58%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>24</t>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>7056</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>7056</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>7056</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>22618</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>16194</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>30943</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>15,79%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>16864</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>11519</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>24149</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>10781</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>23382</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>12,29%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>17,6%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>22618</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>16456</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>31428</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49638</t>
+          <t>49530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>120650</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>112325</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>127074</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>84,21%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>88,7%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>120334</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>113049</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>125679</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>113816</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>126417</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>87,71%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>82,4%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>91,6%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>120650</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>111840</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>126812</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>84,21%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230828</t>
+          <t>230936</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250455</t>
+          <t>249807</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>143268</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>143268</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>143268</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137198</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137198</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137198</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>143268</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>143268</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>143268</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3362,67 +3362,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6571</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>2402</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5200</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5409</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>15,16%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2909</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6542</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14835</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11173</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17049</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>62,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13441</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10643</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15262</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10434</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15234</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>84,84%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14835</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17032</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,6%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>24625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31079</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15843</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15843</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15843</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3705,67 +3705,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2199</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2040</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5034</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4880</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,01%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2199</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6058</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16863</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13562</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18414</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>9956</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6962</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11365</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7116</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>11372</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,99%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>16863</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>13004</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>18409</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,46%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22677</t>
+          <t>22487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29453</t>
+          <t>29061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>11996</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>11996</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>11996</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4048,67 +4048,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4840</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>1931</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4427</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4735</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -4156,72 +4156,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8231</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5427</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9666</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>52,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>6915</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4419</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8285</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4136</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8278</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>49,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8231</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5532</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9647</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,17%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>17655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8846</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>8846</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>8846</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3866</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11729</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8452</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5032</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13419</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4510</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13431</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>18,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7419</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4315</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12436</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22563</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27105</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22795</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30658</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,8%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>38037</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33070</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41457</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33058</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>41979</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>81,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>71,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,18%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27105</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>22088</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>30209</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>78,51%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58450</t>
+          <t>59062</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70044</t>
+          <t>70263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>46489</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>46489</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>46489</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6245</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5072</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8934</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8958</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>19,05%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6245</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10640</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19417</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15453</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22432</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>75,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>60,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>21549</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17687</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24346</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17663</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24226</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>80,95%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>66,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>19417</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>15022</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>22369</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>75,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35173</t>
+          <t>35484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45234</t>
+          <t>45461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>26621</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>26621</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>26621</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2234</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5043</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>22,84%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>51,57%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1206</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3865</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3809</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>9,26%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>29,67%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2234</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5040</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -5185,74 +5185,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7544</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4735</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9141</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>77,16%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>48,43%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>11819</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9160</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>9216</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>90,74%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>70,33%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>70,76%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>7544</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>4738</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>9125</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>77,16%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>48,45%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>28</t>
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21597</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>23042</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>16713</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>30507</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>19,69%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>26,07%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>21104</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>15108</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>28145</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>15160</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>28851</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>17,18%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>22,92%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>23042</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>15819</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>30417</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>19,69%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35094</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54222</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>93993</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>86528</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>100322</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>80,31%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>73,93%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>85,72%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>101716</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>94675</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>107712</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>93969</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>107660</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>82,82%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>77,08%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>87,7%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>93993</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>86618</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>101216</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>80,31%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>185633</t>
+          <t>185885</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>204761</t>
+          <t>204537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>122820</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>122820</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>122820</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2619</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7830</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5540</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2852</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9544</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26221</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21010</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28522</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>19312</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15308</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22000</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>77,71%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23115</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30811</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>45350</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41861</t>
+          <t>39020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52019</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5660</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3710</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4048</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5650</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>989</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -6448,74 +6448,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20764</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16966</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22071</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>22245</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19722</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>21807</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>18928</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22976</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>94,91%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>82,38%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>21394</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>17842</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>22768</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,07%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>75,95%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>61</t>
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>43639</t>
+          <t>42570</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39946</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45581</t>
+          <t>44613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1894</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8411</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3560</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3712</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5303</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9513</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>30,66%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -6791,74 +6791,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10467</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13131</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8489</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6036</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,46%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8428</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5807</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9519</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>61,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11993</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7783</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14911</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>69,34%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>32</t>
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13750</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8246</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23957</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11965</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28765</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,67%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24494</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>26590</t>
+          <t>21160</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>13745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45530</t>
+          <t>32920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25787</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41498</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>72,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>64416</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47616</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>73692</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,33%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41219</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>29652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47235</t>
+          <t>38316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>105635</t>
+          <t>71125</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86695</t>
+          <t>59365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120324</t>
+          <t>78540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>85,11%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4013</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7732</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>6627</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3423</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11024</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22,93%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28157</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>24438</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30445</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>22279</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17882</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>25483</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>77,07%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27428</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>53637</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48004</t>
+          <t>45322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58213</t>
+          <t>54554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7707,72 +7707,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7096</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>24,72%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>50,28%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5038</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2538</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7941</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>41,22%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2586</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7950</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>41,14%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>20,77%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>64,98%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7872</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>27,72%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>12833</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -7820,74 +7820,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10625</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7019</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12878</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>75,28%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>49,72%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>7183</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4280</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9683</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>58,78%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>35,02%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7328</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4499</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9863</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>58,86%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>36,14%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>79,23%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11058</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>7427</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>13889</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>72,28%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>48,54%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>90,78%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>25</t>
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>81,47%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>22247</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>44815</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>18,64%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>31464</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>18614</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>47558</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24664</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48262</t>
+          <t>34520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>64980</t>
+          <t>56860</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48145</t>
+          <t>45871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85329</t>
+          <t>72825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>132227</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>117705</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>140273</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>81,36%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>72,43%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>143923</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>127829</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>156773</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>82,06%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>72,88%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>89,39%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>145793</t>
+          <t>114169</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131047</t>
+          <t>106216</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154645</t>
+          <t>121535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>289717</t>
+          <t>246397</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269368</t>
+          <t>230432</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>306552</t>
+          <t>257386</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>354697</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>354697</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>354697</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
